--- a/data/file_generation/reference/data_200/彩票形态分析Excel_优化版_modified_res.xlsx
+++ b/data/file_generation/reference/data_200/彩票形态分析Excel_优化版_modified_res.xlsx
@@ -2160,18 +2160,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{300DCD27-F73B-4ADF-BA9B-AAB2389D3A4E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5C3CA90-29B8-4876-A897-D40E5FE186C5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66605317-5DC9-4C69-A1E1-0A9EE3AC8FC9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AC12C43-8CFC-4764-99AE-3CE6FD0BA564}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0A04FE2-9B43-4BD4-ACB6-6539DD26B209}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E46D896B-BD0A-41CD-8C59-22FA3286545E}"/>
 </file>